--- a/src/test/resources/LoginValidInvalidCreditional.xlsx
+++ b/src/test/resources/LoginValidInvalidCreditional.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{C75E7F84-BDC6-43B8-B3E3-B6BE5455F74C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{B2E2C5CE-4429-491D-B08C-4EA765BF96E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CD68CCF0-FA11-4AD6-84D7-CD5E4C1B6730}"/>
   </bookViews>
@@ -12,19 +12,10 @@
     <sheet name="InvalidData" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:O18"/>
+  <oleSize ref="A1:O16"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>

--- a/src/test/resources/LoginValidInvalidCreditional.xlsx
+++ b/src/test/resources/LoginValidInvalidCreditional.xlsx
@@ -3,16 +3,18 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{B2E2C5CE-4429-491D-B08C-4EA765BF96E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{BE5E4C2E-B768-4F01-9E9A-70320D8802CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CD68CCF0-FA11-4AD6-84D7-CD5E4C1B6730}"/>
   </bookViews>
   <sheets>
     <sheet name="ValidData" sheetId="1" r:id="rId1"/>
     <sheet name="InvalidData" sheetId="2" r:id="rId2"/>
+    <sheet name="BlankData" sheetId="3" r:id="rId3"/>
+    <sheet name="BoundaryData" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:O16"/>
+  <oleSize ref="A1:N8"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="13">
   <si>
     <t>UserName</t>
   </si>
@@ -58,14 +60,28 @@
   </si>
   <si>
     <t>"12345"</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>aaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaaa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -99,9 +115,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -556,4 +573,90 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{148337A5-9C4F-4F25-8CF7-884ADC87C439}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.6640625" customWidth="1"/>
+    <col min="2" max="2" width="25.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5069914-1A07-4B9A-85AA-EBCFB0E2031B}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="41.44140625" customWidth="1"/>
+    <col min="2" max="2" width="112.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/LoginValidInvalidCreditional.xlsx
+++ b/src/test/resources/LoginValidInvalidCreditional.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{BE5E4C2E-B768-4F01-9E9A-70320D8802CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{FDB3190A-EE7D-41AA-A884-2053B2259C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CD68CCF0-FA11-4AD6-84D7-CD5E4C1B6730}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{CD68CCF0-FA11-4AD6-84D7-CD5E4C1B6730}"/>
   </bookViews>
   <sheets>
     <sheet name="ValidData" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
     <sheet name="BoundaryData" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:N8"/>
+  <oleSize ref="A1:B14"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="12">
   <si>
     <t>UserName</t>
   </si>
@@ -57,9 +57,6 @@
   </si>
   <si>
     <t>wrong_user</t>
-  </si>
-  <si>
-    <t>"12345"</t>
   </si>
   <si>
     <t>a</t>
@@ -554,22 +551,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-    </row>
+    <row r="5" spans="1:2" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:2" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -626,7 +609,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -637,12 +620,12 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -653,7 +636,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
